--- a/HSI_FSC_result/4. C Way/score_25way.xlsx
+++ b/HSI_FSC_result/4. C Way/score_25way.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_4_25way\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\DevelopProject\Develop_DeepLearning\HSI\HSI-FSC\HSI_FSC_result\4. C Way\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71327E6-0876-4EF6-BEEA-E0EE0673779D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFBBAEA-3340-4E7E-B183-3D82AA8788AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="1260" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12885" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IP" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -79,7 +86,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -358,9 +365,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>28.125</v>
       </c>
@@ -396,7 +403,7 @@
         <v>38.525363900000002</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>53.745925999999997</v>
       </c>
@@ -432,7 +439,7 @@
         <v>48.318376500000007</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>64.073229999999995</v>
       </c>
@@ -468,7 +475,7 @@
         <v>43.336334699999995</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>67.17792</v>
       </c>
@@ -504,7 +511,7 @@
         <v>47.071541199999999</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>33.843018000000001</v>
       </c>
@@ -540,7 +547,7 @@
         <v>62.175457399999992</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>90.550070000000005</v>
       </c>
@@ -576,7 +583,7 @@
         <v>84.776094499999985</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>30.769231999999999</v>
       </c>
@@ -612,7 +619,7 @@
         <v>35.905519100000006</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>96.666663999999997</v>
       </c>
@@ -648,7 +655,7 @@
         <v>93.730501799999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>9.6618359999999992</v>
       </c>
@@ -684,7 +691,7 @@
         <v>18.6314724</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>50.539290000000001</v>
       </c>
@@ -720,7 +727,7 @@
         <v>47.443612600000009</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>75</v>
       </c>
@@ -756,7 +763,7 @@
         <v>72.406773199999989</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>16.915759999999999</v>
       </c>
@@ -792,7 +799,7 @@
         <v>35.791753200000002</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>88.596500000000006</v>
       </c>
@@ -828,7 +835,7 @@
         <v>70.034396700000002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>93.582886000000002</v>
       </c>
@@ -864,7 +871,7 @@
         <v>92.346022599999998</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>33.138855</v>
       </c>
@@ -900,7 +907,7 @@
         <v>50.867064999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>32.068966000000003</v>
       </c>
@@ -936,7 +943,7 @@
         <v>48.905962100000004</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>51.868474973168098</v>
       </c>
@@ -972,7 +979,7 @@
         <v>56.832861742608976</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>54.028445482254</v>
       </c>
@@ -1008,7 +1015,7 @@
         <v>55.641638934612232</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>47.110330153518497</v>
       </c>
@@ -1045,6 +1052,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1053,9 +1061,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C6D9CA-287C-4A13-BF9B-099121023619}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>66.874679999999998</v>
       </c>
@@ -1068,7 +1076,7 @@
       <c r="D1">
         <v>94.274990000000003</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="1">
         <v>96.432019999999994</v>
       </c>
       <c r="F1">
@@ -1087,11 +1095,11 @@
         <v>65.944879999999998</v>
       </c>
       <c r="K1" s="1">
-        <f>AVERAGE(A1:J1)</f>
+        <f t="shared" ref="K1:K19" si="0">AVERAGE(A1:J1)</f>
         <v>83.424164000000005</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>76.102485999999999</v>
       </c>
@@ -1104,7 +1112,7 @@
       <c r="D2">
         <v>99.805449999999993</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>98.748639999999995</v>
       </c>
       <c r="F2">
@@ -1123,11 +1131,11 @@
         <v>76.089550000000003</v>
       </c>
       <c r="K2" s="1">
-        <f>AVERAGE(A2:J2)</f>
+        <f t="shared" si="0"/>
         <v>88.292749599999993</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>89.787430000000001</v>
       </c>
@@ -1140,7 +1148,7 @@
       <c r="D3">
         <v>54.414610000000003</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>68.80489</v>
       </c>
       <c r="F3">
@@ -1159,11 +1167,11 @@
         <v>95.158919999999995</v>
       </c>
       <c r="K3" s="1">
-        <f>AVERAGE(A3:J3)</f>
+        <f t="shared" si="0"/>
         <v>87.221488999999991</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>92.491690000000006</v>
       </c>
@@ -1176,7 +1184,7 @@
       <c r="D4">
         <v>78.935450000000003</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>87.949523999999997</v>
       </c>
       <c r="F4">
@@ -1195,11 +1203,11 @@
         <v>97.482519999999994</v>
       </c>
       <c r="K4" s="1">
-        <f>AVERAGE(A4:J4)</f>
+        <f t="shared" si="0"/>
         <v>92.617923300000001</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>99.497479999999996</v>
       </c>
@@ -1212,7 +1220,7 @@
       <c r="D5">
         <v>97.836100000000002</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>99.830290000000005</v>
       </c>
       <c r="F5">
@@ -1231,11 +1239,11 @@
         <v>98.36936</v>
       </c>
       <c r="K5" s="1">
-        <f>AVERAGE(A5:J5)</f>
+        <f t="shared" si="0"/>
         <v>97.379429599999995</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>100</v>
       </c>
@@ -1248,7 +1256,7 @@
       <c r="D6">
         <v>98.546004999999994</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>93.085599999999999</v>
       </c>
       <c r="F6">
@@ -1267,11 +1275,11 @@
         <v>91.254220000000004</v>
       </c>
       <c r="K6" s="1">
-        <f>AVERAGE(A6:J6)</f>
+        <f t="shared" si="0"/>
         <v>95.909703899999997</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>99.749020000000002</v>
       </c>
@@ -1284,7 +1292,7 @@
       <c r="D7">
         <v>91.387314000000003</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>96.599189999999993</v>
       </c>
       <c r="F7">
@@ -1303,11 +1311,11 @@
         <v>96.671580000000006</v>
       </c>
       <c r="K7" s="1">
-        <f>AVERAGE(A7:J7)</f>
+        <f t="shared" si="0"/>
         <v>94.096103999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>84.589230000000001</v>
       </c>
@@ -1320,7 +1328,7 @@
       <c r="D8">
         <v>92.095375000000004</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>89.763019999999997</v>
       </c>
       <c r="F8">
@@ -1339,11 +1347,11 @@
         <v>81.099530000000001</v>
       </c>
       <c r="K8" s="1">
-        <f>AVERAGE(A8:J8)</f>
+        <f t="shared" si="0"/>
         <v>88.146100599999997</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>99.289749999999998</v>
       </c>
@@ -1356,7 +1364,7 @@
       <c r="D9">
         <v>100</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>93.509690000000006</v>
       </c>
       <c r="F9">
@@ -1375,11 +1383,11 @@
         <v>99.902879999999996</v>
       </c>
       <c r="K9" s="1">
-        <f>AVERAGE(A9:J9)</f>
+        <f t="shared" si="0"/>
         <v>97.752634599999993</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>96.167559999999995</v>
       </c>
@@ -1392,7 +1400,7 @@
       <c r="D10">
         <v>75.012550000000005</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>91.921906000000007</v>
       </c>
       <c r="F10">
@@ -1411,11 +1419,11 @@
         <v>80.345249999999993</v>
       </c>
       <c r="K10" s="1">
-        <f>AVERAGE(A10:J10)</f>
+        <f t="shared" si="0"/>
         <v>90.571393300000011</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>99.434494000000001</v>
       </c>
@@ -1428,7 +1436,7 @@
       <c r="D11">
         <v>79.924239999999998</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>97.918729999999996</v>
       </c>
       <c r="F11">
@@ -1447,11 +1455,11 @@
         <v>98.736639999999994</v>
       </c>
       <c r="K11" s="1">
-        <f>AVERAGE(A11:J11)</f>
+        <f t="shared" si="0"/>
         <v>93.487032899999988</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>99.17492</v>
       </c>
@@ -1464,7 +1472,7 @@
       <c r="D12">
         <v>91.362759999999994</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>99.446594000000005</v>
       </c>
       <c r="F12">
@@ -1483,11 +1491,11 @@
         <v>99.893394000000001</v>
       </c>
       <c r="K12" s="1">
-        <f>AVERAGE(A12:J12)</f>
+        <f t="shared" si="0"/>
         <v>97.394756200000003</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>78.387649999999994</v>
       </c>
@@ -1500,7 +1508,7 @@
       <c r="D13">
         <v>95.948830000000001</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>91.700400000000002</v>
       </c>
       <c r="F13">
@@ -1519,11 +1527,11 @@
         <v>94.483733999999998</v>
       </c>
       <c r="K13" s="1">
-        <f>AVERAGE(A13:J13)</f>
+        <f t="shared" si="0"/>
         <v>81.305561600000004</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>97.304829999999995</v>
       </c>
@@ -1536,7 +1544,7 @@
       <c r="D14">
         <v>82.244420000000005</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>84.485534999999999</v>
       </c>
       <c r="F14">
@@ -1555,11 +1563,11 @@
         <v>80.075190000000006</v>
       </c>
       <c r="K14" s="1">
-        <f>AVERAGE(A14:J14)</f>
+        <f t="shared" si="0"/>
         <v>76.36363320000001</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>76.015050000000002</v>
       </c>
@@ -1572,7 +1580,7 @@
       <c r="D15">
         <v>70.708460000000002</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>66.238845999999995</v>
       </c>
       <c r="F15">
@@ -1591,11 +1599,11 @@
         <v>71.198670000000007</v>
       </c>
       <c r="K15" s="1">
-        <f>AVERAGE(A15:J15)</f>
+        <f t="shared" si="0"/>
         <v>69.350863799999999</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>100</v>
       </c>
@@ -1608,7 +1616,7 @@
       <c r="D16">
         <v>98.690290000000005</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>99.787689999999998</v>
       </c>
       <c r="F16">
@@ -1627,11 +1635,11 @@
         <v>100</v>
       </c>
       <c r="K16" s="1">
-        <f>AVERAGE(A16:J16)</f>
+        <f t="shared" si="0"/>
         <v>93.986879000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>88.983724066581601</v>
       </c>
@@ -1644,7 +1652,7 @@
       <c r="D17">
         <v>86.596833490365597</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>87.599992610245806</v>
       </c>
       <c r="F17">
@@ -1663,11 +1671,11 @@
         <v>86.177464944853895</v>
       </c>
       <c r="K17" s="1">
-        <f>AVERAGE(A17:J17)</f>
+        <f t="shared" si="0"/>
         <v>86.998281882170318</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>90.929138660430894</v>
       </c>
@@ -1680,7 +1688,7 @@
       <c r="D18">
         <v>87.574177980422903</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>91.013908386230398</v>
       </c>
       <c r="F18">
@@ -1699,11 +1707,11 @@
         <v>89.1691446304321</v>
       </c>
       <c r="K18" s="1">
-        <f>AVERAGE(A18:J18)</f>
+        <f t="shared" si="0"/>
         <v>89.206274747848482</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>87.740851761530806</v>
       </c>
@@ -1716,7 +1724,7 @@
       <c r="D19">
         <v>85.171065762003295</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>86.258266085380797</v>
       </c>
       <c r="F19">
@@ -1735,11 +1743,12 @@
         <v>84.598697472031702</v>
       </c>
       <c r="K19" s="1">
-        <f>AVERAGE(A19:J19)</f>
+        <f t="shared" si="0"/>
         <v>85.583565454835906</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -1748,9 +1757,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BF268C6-262B-4B5D-895F-55B8B1A5BC12}">
   <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>85.928139999999999</v>
       </c>
@@ -1786,7 +1795,7 @@
         <v>89.847771100000003</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>91.335570000000004</v>
       </c>
@@ -1822,7 +1831,7 @@
         <v>92.857272899999998</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>62.614677</v>
       </c>
@@ -1858,7 +1867,7 @@
         <v>60.560537199999999</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>77.317374999999998</v>
       </c>
@@ -1894,7 +1903,7 @@
         <v>76.174121700000001</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>98.525069999999999</v>
       </c>
@@ -1930,7 +1939,7 @@
         <v>92.593043399999985</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>40.117516000000002</v>
       </c>
@@ -1966,7 +1975,7 @@
         <v>43.474356599999993</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>35.07329</v>
       </c>
@@ -2002,7 +2011,7 @@
         <v>50.989856199999998</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>68.411995000000005</v>
       </c>
@@ -2038,7 +2047,7 @@
         <v>69.025959200000003</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>81.076065</v>
       </c>
@@ -2074,7 +2083,7 @@
         <v>64.368600799999996</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>73.162521039835397</v>
       </c>
@@ -2110,7 +2119,7 @@
         <v>72.462829624088229</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>71.155524253845201</v>
       </c>
@@ -2146,7 +2155,7 @@
         <v>71.099057197570772</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>65.839960996984999</v>
       </c>
@@ -2183,6 +2192,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2190,8 +2200,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B3FC5D-CBEF-4852-9492-3A8AFB021ED5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2199,8 +2210,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0042C639-A362-44FB-9C81-3BA17FB792FE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>